--- a/app/file/fu_data staf.xlsx
+++ b/app/file/fu_data staf.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Apl Program\File Aplikasi\xampp\htdocs\siap\app\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D707140-ED4A-43F4-BB7A-168D1F9725FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73023972-2B5B-4FFA-9309-E68B3D859030}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{40E330D0-0F53-437F-83B6-A86DDF516292}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
   <si>
     <t>No</t>
   </si>
@@ -65,9 +65,6 @@
     <t>Pendidikan Terakhir</t>
   </si>
   <si>
-    <t>Gelar</t>
-  </si>
-  <si>
     <t>NIP</t>
   </si>
   <si>
@@ -165,6 +162,12 @@
   </si>
   <si>
     <t>ID Staf</t>
+  </si>
+  <si>
+    <t>Gelar Belakang</t>
+  </si>
+  <si>
+    <t>Gelar Depan</t>
   </si>
 </sst>
 </file>
@@ -588,7 +591,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9862070E-A880-4BD9-BE26-6A27396E22FB}">
-  <dimension ref="A1:AQ1"/>
+  <dimension ref="A1:AR1"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.5703125" style="5" bestFit="1" customWidth="1"/>
@@ -599,49 +602,49 @@
     <col min="8" max="8" width="4.28515625" style="5" customWidth="1"/>
     <col min="9" max="9" width="21" style="5" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="12.85546875" style="6" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.28515625" style="5" customWidth="1"/>
-    <col min="12" max="12" width="5.7109375" style="5" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="16.28515625" style="5" customWidth="1"/>
-    <col min="14" max="14" width="25" style="5" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="20.28515625" style="5" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="7.140625" style="5" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="47.7109375" style="5" customWidth="1"/>
-    <col min="18" max="18" width="3.140625" style="5" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="3.85546875" style="5" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="6.7109375" style="5" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="21" style="5" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="23.85546875" style="5" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="9.140625" style="5" customWidth="1"/>
-    <col min="24" max="24" width="8" style="5" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="13.140625" style="5" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="30.140625" style="5" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="20.42578125" style="5" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="22.140625" style="5" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="13.28515625" style="6" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="25" style="5" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="17.85546875" style="6" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="22.42578125" style="5" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="17.42578125" style="5" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="13.42578125" style="5" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="18.28515625" style="5" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="17.5703125" style="5" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="20.7109375" style="5" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="19.28515625" style="5" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="21.85546875" style="5" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="10.42578125" style="6" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="20.5703125" style="5" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="17.7109375" style="5" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="17.28515625" style="5" bestFit="1" customWidth="1"/>
-    <col min="44" max="59" width="9.140625" style="4" customWidth="1"/>
-    <col min="60" max="16384" width="9.140625" style="4"/>
+    <col min="11" max="12" width="11.28515625" style="5" customWidth="1"/>
+    <col min="13" max="13" width="11.140625" style="5" customWidth="1"/>
+    <col min="14" max="14" width="16.28515625" style="5" customWidth="1"/>
+    <col min="15" max="15" width="25" style="5" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="20.28515625" style="5" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="47.7109375" style="5" customWidth="1"/>
+    <col min="19" max="19" width="3.140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="3.85546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="6.7109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="21" style="5" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="23.85546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="9.140625" style="5" customWidth="1"/>
+    <col min="25" max="25" width="8" style="5" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="13.140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="30.140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="20.42578125" style="5" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="22.140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="13.28515625" style="6" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="25" style="5" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="17.85546875" style="6" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="22.42578125" style="5" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="17.42578125" style="5" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="13.42578125" style="5" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="18.28515625" style="5" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="17.5703125" style="5" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="20.7109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="19.28515625" style="5" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="21.85546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="10.42578125" style="6" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="20.5703125" style="5" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="17.7109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="17.28515625" style="5" bestFit="1" customWidth="1"/>
+    <col min="45" max="60" width="9.140625" style="4" customWidth="1"/>
+    <col min="61" max="16384" width="9.140625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:43" s="3" customFormat="1" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:44" s="3" customFormat="1" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
@@ -656,7 +659,7 @@
         <v>4</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>5</v>
@@ -671,110 +674,113 @@
         <v>8</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="N1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="P1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AD1" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AC1" s="2" t="s">
+      <c r="AE1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AF1" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="AE1" s="2" t="s">
+      <c r="AG1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AH1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AI1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AJ1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="AI1" s="1" t="s">
+      <c r="AK1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AJ1" s="1" t="s">
+      <c r="AL1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AK1" s="1" t="s">
+      <c r="AM1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="AL1" s="1" t="s">
+      <c r="AN1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="AM1" s="1" t="s">
+      <c r="AO1" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="AN1" s="2" t="s">
+      <c r="AP1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AO1" s="1" t="s">
+      <c r="AQ1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="AP1" s="1" t="s">
+      <c r="AR1" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="AQ1" s="1" t="s">
-        <v>40</v>
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="qg4EfAknOuHp8nQsE0lfoFeKpkr7h+2Q+hZ47goREsPQolEYSRm3Y3AbzZOHiORQb68wJ4vsY47ZbpSYc5uWaQ==" saltValue="jHNYFQCOhRRsQhFUsozIyQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" insertRows="0" selectLockedCells="1" sort="0"/>
+  <sheetProtection insertRows="0" selectLockedCells="1" sort="0"/>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="Peringatan" error="Data yang anda pilih tidak sesuai" promptTitle="Info" prompt="Silahkan pilih data yang sudah disediakan" sqref="O2:O1048576" xr:uid="{9596709A-8209-49E8-89E4-4F872E7E9A35}">
+    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="Peringatan" error="Data yang anda pilih tidak sesuai" promptTitle="Info" prompt="Silahkan pilih data yang sudah disediakan" sqref="P2:P1048576" xr:uid="{9596709A-8209-49E8-89E4-4F872E7E9A35}">
       <formula1>"Guru,Tendik,Kepsek,KTAS"</formula1>
     </dataValidation>
-    <dataValidation showInputMessage="1" showErrorMessage="1" errorTitle="Peringatan" error="Data yang anda pilih tidak sesuai" promptTitle="Info" prompt="Silahkan pilih data yang sudah disediakan" sqref="O1" xr:uid="{2E659902-A2A7-400D-8752-9468B6418C41}"/>
+    <dataValidation showInputMessage="1" showErrorMessage="1" errorTitle="Peringatan" error="Data yang anda pilih tidak sesuai" promptTitle="Info" prompt="Silahkan pilih data yang sudah disediakan" sqref="P1" xr:uid="{2E659902-A2A7-400D-8752-9468B6418C41}"/>
     <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="Peringatan" error="Data tidak sesuai" promptTitle="Info" prompt="Silahkan pilih data yang sudah disediakan" sqref="H2:H1048576" xr:uid="{203DE40F-A5E7-4744-9ACA-C3401220A394}">
       <formula1>"L,P"</formula1>
     </dataValidation>
